--- a/artfynd/A 39284-2024 artfynd.xlsx
+++ b/artfynd/A 39284-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119816555</v>
+        <v>119816534</v>
       </c>
       <c r="B2" t="n">
-        <v>94681</v>
+        <v>57463</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581743</v>
+        <v>581771</v>
       </c>
       <c r="R2" t="n">
-        <v>6414418</v>
+        <v>6414420</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -763,7 +771,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -782,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119816534</v>
+        <v>119816497</v>
       </c>
       <c r="B3" t="n">
-        <v>57463</v>
+        <v>96865</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,39 +801,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>221946</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,13 +841,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581771</v>
+        <v>581780</v>
       </c>
       <c r="R3" t="n">
-        <v>6414420</v>
+        <v>6414421</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,6 +885,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -896,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119816497</v>
+        <v>119816555</v>
       </c>
       <c r="B4" t="n">
-        <v>96865</v>
+        <v>94681</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,33 +920,25 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221946</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581780</v>
+        <v>581743</v>
       </c>
       <c r="R4" t="n">
-        <v>6414421</v>
+        <v>6414418</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 39284-2024 artfynd.xlsx
+++ b/artfynd/A 39284-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119816534</v>
+        <v>119816555</v>
       </c>
       <c r="B2" t="n">
-        <v>57463</v>
+        <v>94681</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581771</v>
+        <v>581743</v>
       </c>
       <c r="R2" t="n">
-        <v>6414420</v>
+        <v>6414418</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,6 +763,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -904,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119816555</v>
+        <v>119816534</v>
       </c>
       <c r="B4" t="n">
-        <v>94681</v>
+        <v>57463</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,31 +909,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -948,13 +949,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581743</v>
+        <v>581771</v>
       </c>
       <c r="R4" t="n">
-        <v>6414418</v>
+        <v>6414420</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,7 +993,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 39284-2024 artfynd.xlsx
+++ b/artfynd/A 39284-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>119816555</v>
       </c>
       <c r="B2" t="n">
-        <v>94681</v>
+        <v>94704</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119816497</v>
+        <v>119816534</v>
       </c>
       <c r="B3" t="n">
-        <v>96865</v>
+        <v>57473</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,39 +794,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221946</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,13 +834,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581780</v>
+        <v>581771</v>
       </c>
       <c r="R3" t="n">
-        <v>6414421</v>
+        <v>6414420</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,7 +878,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -897,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119816534</v>
+        <v>119816497</v>
       </c>
       <c r="B4" t="n">
-        <v>57463</v>
+        <v>96888</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,39 +908,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>221946</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -949,13 +948,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581771</v>
+        <v>581780</v>
       </c>
       <c r="R4" t="n">
-        <v>6414420</v>
+        <v>6414421</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -993,6 +992,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 39284-2024 artfynd.xlsx
+++ b/artfynd/A 39284-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119816555</v>
+        <v>119816534</v>
       </c>
       <c r="B2" t="n">
-        <v>94704</v>
+        <v>57473</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581743</v>
+        <v>581771</v>
       </c>
       <c r="R2" t="n">
-        <v>6414418</v>
+        <v>6414420</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -763,7 +771,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -782,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119816534</v>
+        <v>119816497</v>
       </c>
       <c r="B3" t="n">
-        <v>57473</v>
+        <v>96888</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,39 +801,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>221946</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,13 +841,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581771</v>
+        <v>581780</v>
       </c>
       <c r="R3" t="n">
-        <v>6414420</v>
+        <v>6414421</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,6 +885,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -896,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119816497</v>
+        <v>119816555</v>
       </c>
       <c r="B4" t="n">
-        <v>96888</v>
+        <v>94704</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,33 +920,25 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221946</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581780</v>
+        <v>581743</v>
       </c>
       <c r="R4" t="n">
-        <v>6414421</v>
+        <v>6414418</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 39284-2024 artfynd.xlsx
+++ b/artfynd/A 39284-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119816534</v>
+        <v>119816555</v>
       </c>
       <c r="B2" t="n">
-        <v>57473</v>
+        <v>94704</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581771</v>
+        <v>581743</v>
       </c>
       <c r="R2" t="n">
-        <v>6414420</v>
+        <v>6414418</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,6 +763,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -904,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119816555</v>
+        <v>119816534</v>
       </c>
       <c r="B4" t="n">
-        <v>94704</v>
+        <v>57473</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,31 +909,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -948,13 +949,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581743</v>
+        <v>581771</v>
       </c>
       <c r="R4" t="n">
-        <v>6414418</v>
+        <v>6414420</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,7 +993,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
